--- a/projects/paper-01/04-extract/数据_6_数据提取表_v2.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v2.xlsx
@@ -1144,7 +1144,11 @@
       <c r="K3" s="6" t="n">
         <v>67.93000000000001</v>
       </c>
-      <c r="L3" s="6" t="n"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M3" s="6" t="n">
         <v>5.57</v>
       </c>
@@ -1337,7 +1341,11 @@
       <c r="K4" s="6" t="n">
         <v>69.23999999999999</v>
       </c>
-      <c r="L4" s="6" t="n"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M4" s="6" t="n">
         <v>3.1</v>
       </c>
@@ -1482,7 +1490,9 @@
       <c r="AV4" s="6" t="n"/>
       <c r="AW4" s="6" t="n"/>
       <c r="AX4" s="6" t="n"/>
-      <c r="AY4" s="6" t="n"/>
+      <c r="AY4" s="6" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -1524,7 +1534,11 @@
       <c r="K5" s="6" t="n">
         <v>64.8</v>
       </c>
-      <c r="L5" s="6" t="n"/>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="n">
         <v>5.1</v>
       </c>
@@ -1717,7 +1731,11 @@
       <c r="K6" s="6" t="n">
         <v>64.38</v>
       </c>
-      <c r="L6" s="6" t="n"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M6" s="6" t="n">
         <v>5.08</v>
       </c>
@@ -1860,7 +1878,9 @@
       <c r="AV6" s="6" t="n"/>
       <c r="AW6" s="6" t="n"/>
       <c r="AX6" s="6" t="n"/>
-      <c r="AY6" s="6" t="n"/>
+      <c r="AY6" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -1902,7 +1922,11 @@
       <c r="K7" s="6" t="n">
         <v>63.11</v>
       </c>
-      <c r="L7" s="6" t="n"/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -2057,7 +2081,9 @@
       <c r="AV7" s="6" t="n"/>
       <c r="AW7" s="6" t="n"/>
       <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
+      <c r="AY7" s="6" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -2099,7 +2125,11 @@
       <c r="K8" s="6" t="n">
         <v>67.17</v>
       </c>
-      <c r="L8" s="6" t="n"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="n">
         <v>4.4</v>
       </c>
@@ -2246,7 +2276,9 @@
       <c r="AV8" s="6" t="n"/>
       <c r="AW8" s="6" t="n"/>
       <c r="AX8" s="6" t="n"/>
-      <c r="AY8" s="6" t="n"/>
+      <c r="AY8" s="6" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -2449,7 +2481,9 @@
       <c r="AV9" s="6" t="n"/>
       <c r="AW9" s="6" t="n"/>
       <c r="AX9" s="6" t="n"/>
-      <c r="AY9" s="6" t="n"/>
+      <c r="AY9" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -2491,7 +2525,11 @@
       <c r="K10" s="6" t="n">
         <v>70.34999999999999</v>
       </c>
-      <c r="L10" s="6" t="n"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="n">
         <v>3.66</v>
       </c>
@@ -2642,7 +2680,9 @@
       <c r="AV10" s="6" t="n"/>
       <c r="AW10" s="6" t="n"/>
       <c r="AX10" s="6" t="n"/>
-      <c r="AY10" s="6" t="n"/>
+      <c r="AY10" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -2684,7 +2724,11 @@
       <c r="K11" s="6" t="n">
         <v>68.2</v>
       </c>
-      <c r="L11" s="6" t="n"/>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n">
         <v>5.92</v>
       </c>
@@ -2835,7 +2879,9 @@
       <c r="AV11" s="6" t="n"/>
       <c r="AW11" s="6" t="n"/>
       <c r="AX11" s="6" t="n"/>
-      <c r="AY11" s="6" t="n"/>
+      <c r="AY11" s="6" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -2877,7 +2923,11 @@
       <c r="K12" s="6" t="n">
         <v>64.95999999999999</v>
       </c>
-      <c r="L12" s="6" t="n"/>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n">
         <v>3.77</v>
       </c>
@@ -3028,7 +3078,9 @@
       <c r="AV12" s="6" t="n"/>
       <c r="AW12" s="6" t="n"/>
       <c r="AX12" s="6" t="n"/>
-      <c r="AY12" s="6" t="n"/>
+      <c r="AY12" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -3070,7 +3122,11 @@
       <c r="K13" s="6" t="n">
         <v>69.03</v>
       </c>
-      <c r="L13" s="6" t="n"/>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -3225,7 +3281,9 @@
       <c r="AV13" s="6" t="n"/>
       <c r="AW13" s="6" t="n"/>
       <c r="AX13" s="6" t="n"/>
-      <c r="AY13" s="6" t="n"/>
+      <c r="AY13" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -3422,7 +3480,9 @@
       <c r="AV14" s="6" t="n"/>
       <c r="AW14" s="6" t="n"/>
       <c r="AX14" s="6" t="n"/>
-      <c r="AY14" s="6" t="n"/>
+      <c r="AY14" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -3464,7 +3524,11 @@
       <c r="K15" s="6" t="n">
         <v>68.84</v>
       </c>
-      <c r="L15" s="6" t="n"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n">
         <v>4.65</v>
       </c>
@@ -3615,7 +3679,9 @@
       <c r="AV15" s="6" t="n"/>
       <c r="AW15" s="6" t="n"/>
       <c r="AX15" s="6" t="n"/>
-      <c r="AY15" s="6" t="n"/>
+      <c r="AY15" s="6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
@@ -3808,7 +3874,9 @@
       <c r="AV16" s="6" t="n"/>
       <c r="AW16" s="6" t="n"/>
       <c r="AX16" s="6" t="n"/>
-      <c r="AY16" s="6" t="n"/>
+      <c r="AY16" s="6" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -3850,7 +3918,11 @@
       <c r="K17" s="6" t="n">
         <v>66.7</v>
       </c>
-      <c r="L17" s="6" t="n"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -4003,7 +4075,9 @@
       <c r="AV17" s="6" t="n"/>
       <c r="AW17" s="6" t="n"/>
       <c r="AX17" s="6" t="n"/>
-      <c r="AY17" s="6" t="n"/>
+      <c r="AY17" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -4045,7 +4119,11 @@
       <c r="K18" s="6" t="n">
         <v>66.06999999999999</v>
       </c>
-      <c r="L18" s="6" t="n"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n">
         <v>4.68</v>
       </c>
@@ -4192,7 +4270,9 @@
       <c r="AV18" s="6" t="n"/>
       <c r="AW18" s="6" t="n"/>
       <c r="AX18" s="6" t="n"/>
-      <c r="AY18" s="6" t="n"/>
+      <c r="AY18" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -4387,7 +4467,9 @@
       <c r="AV19" s="6" t="n"/>
       <c r="AW19" s="6" t="n"/>
       <c r="AX19" s="6" t="n"/>
-      <c r="AY19" s="6" t="n"/>
+      <c r="AY19" s="6" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -4429,7 +4511,11 @@
       <c r="K20" s="6" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="L20" s="6" t="n"/>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n">
         <v>5.89</v>
       </c>
@@ -4574,7 +4660,9 @@
       <c r="AV20" s="6" t="n"/>
       <c r="AW20" s="6" t="n"/>
       <c r="AX20" s="6" t="n"/>
-      <c r="AY20" s="6" t="n"/>
+      <c r="AY20" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -4616,7 +4704,11 @@
       <c r="K21" s="6" t="n">
         <v>68.55</v>
       </c>
-      <c r="L21" s="6" t="n"/>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n">
         <v>5.74</v>
       </c>
@@ -4765,7 +4857,9 @@
       <c r="AV21" s="6" t="n"/>
       <c r="AW21" s="6" t="n"/>
       <c r="AX21" s="6" t="n"/>
-      <c r="AY21" s="6" t="n"/>
+      <c r="AY21" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -4807,7 +4901,11 @@
       <c r="K22" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="L22" s="6" t="n"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n">
         <v>4.6</v>
       </c>
@@ -4958,7 +5056,9 @@
       <c r="AV22" s="6" t="n"/>
       <c r="AW22" s="6" t="n"/>
       <c r="AX22" s="6" t="n"/>
-      <c r="AY22" s="6" t="n"/>
+      <c r="AY22" s="6" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -5159,7 +5259,9 @@
       <c r="AV23" s="6" t="n"/>
       <c r="AW23" s="6" t="n"/>
       <c r="AX23" s="6" t="n"/>
-      <c r="AY23" s="6" t="n"/>
+      <c r="AY23" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
@@ -5201,7 +5303,11 @@
       <c r="K24" s="6" t="n">
         <v>68.2</v>
       </c>
-      <c r="L24" s="6" t="n"/>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M24" s="6" t="n">
         <v>3</v>
       </c>
@@ -5344,7 +5450,9 @@
       <c r="AV24" s="6" t="n"/>
       <c r="AW24" s="6" t="n"/>
       <c r="AX24" s="6" t="n"/>
-      <c r="AY24" s="6" t="n"/>
+      <c r="AY24" s="6" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -5386,7 +5494,11 @@
       <c r="K25" s="6" t="n">
         <v>77.2</v>
       </c>
-      <c r="L25" s="6" t="n"/>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>old-old</t>
+        </is>
+      </c>
       <c r="M25" s="6" t="n">
         <v>8.1</v>
       </c>
@@ -5533,7 +5645,9 @@
       <c r="AV25" s="6" t="n"/>
       <c r="AW25" s="6" t="n"/>
       <c r="AX25" s="6" t="n"/>
-      <c r="AY25" s="6" t="n"/>
+      <c r="AY25" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
@@ -5575,7 +5689,11 @@
       <c r="K26" s="6" t="n">
         <v>80.5</v>
       </c>
-      <c r="L26" s="6" t="n"/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>old-old</t>
+        </is>
+      </c>
       <c r="M26" s="6" t="n">
         <v>6.4</v>
       </c>
@@ -5722,7 +5840,9 @@
       <c r="AV26" s="6" t="n"/>
       <c r="AW26" s="6" t="n"/>
       <c r="AX26" s="6" t="n"/>
-      <c r="AY26" s="6" t="n"/>
+      <c r="AY26" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -5764,7 +5884,11 @@
       <c r="K27" s="6" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="L27" s="6" t="n"/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M27" s="6" t="n">
         <v>3.55</v>
       </c>
@@ -5913,7 +6037,9 @@
       <c r="AV27" s="6" t="n"/>
       <c r="AW27" s="6" t="n"/>
       <c r="AX27" s="6" t="n"/>
-      <c r="AY27" s="6" t="n"/>
+      <c r="AY27" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -6154,7 +6280,11 @@
       <c r="K29" s="6" t="n">
         <v>70.8</v>
       </c>
-      <c r="L29" s="6" t="n"/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M29" s="6" t="n">
         <v>5.2</v>
       </c>
@@ -6343,7 +6473,11 @@
       <c r="K30" s="6" t="n">
         <v>69.5</v>
       </c>
-      <c r="L30" s="6" t="n"/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M30" s="6" t="n">
         <v>3</v>
       </c>
@@ -6488,7 +6622,9 @@
       <c r="AV30" s="6" t="n"/>
       <c r="AW30" s="6" t="n"/>
       <c r="AX30" s="6" t="n"/>
-      <c r="AY30" s="6" t="n"/>
+      <c r="AY30" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -6530,7 +6666,11 @@
       <c r="K31" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="L31" s="6" t="n"/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M31" s="6" t="n">
         <v>3.5</v>
       </c>
@@ -6677,7 +6817,9 @@
       <c r="AV31" s="6" t="n"/>
       <c r="AW31" s="6" t="n"/>
       <c r="AX31" s="6" t="n"/>
-      <c r="AY31" s="6" t="n"/>
+      <c r="AY31" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -6719,7 +6861,11 @@
       <c r="K32" s="6" t="n">
         <v>69.7</v>
       </c>
-      <c r="L32" s="6" t="n"/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M32" s="6" t="n">
         <v>4.5</v>
       </c>
@@ -6858,7 +7004,9 @@
       <c r="AV32" s="6" t="n"/>
       <c r="AW32" s="6" t="n"/>
       <c r="AX32" s="6" t="n"/>
-      <c r="AY32" s="6" t="n"/>
+      <c r="AY32" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -6900,7 +7048,11 @@
       <c r="K33" s="6" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="L33" s="6" t="n"/>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M33" s="6" t="n">
         <v>6.1</v>
       </c>
@@ -7041,7 +7193,9 @@
       <c r="AV33" s="6" t="n"/>
       <c r="AW33" s="6" t="n"/>
       <c r="AX33" s="6" t="n"/>
-      <c r="AY33" s="6" t="n"/>
+      <c r="AY33" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -7083,7 +7237,11 @@
       <c r="K34" s="6" t="n">
         <v>83.5</v>
       </c>
-      <c r="L34" s="6" t="n"/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>old-old</t>
+        </is>
+      </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -7230,7 +7388,9 @@
       <c r="AV34" s="6" t="n"/>
       <c r="AW34" s="6" t="n"/>
       <c r="AX34" s="6" t="n"/>
-      <c r="AY34" s="6" t="n"/>
+      <c r="AY34" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -7272,7 +7432,11 @@
       <c r="K35" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="L35" s="6" t="n"/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="n">
         <v>7</v>
       </c>
@@ -7419,7 +7583,9 @@
       <c r="AV35" s="6" t="n"/>
       <c r="AW35" s="6" t="n"/>
       <c r="AX35" s="6" t="n"/>
-      <c r="AY35" s="6" t="n"/>
+      <c r="AY35" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -7461,7 +7627,11 @@
       <c r="K36" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="L36" s="6" t="n"/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>old-old</t>
+        </is>
+      </c>
       <c r="M36" s="6" t="n">
         <v>3.6</v>
       </c>
@@ -7606,7 +7776,9 @@
       <c r="AV36" s="6" t="n"/>
       <c r="AW36" s="6" t="n"/>
       <c r="AX36" s="6" t="n"/>
-      <c r="AY36" s="6" t="n"/>
+      <c r="AY36" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -7648,7 +7820,11 @@
       <c r="K37" s="6" t="n">
         <v>65.89</v>
       </c>
-      <c r="L37" s="6" t="n"/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M37" s="6" t="n">
         <v>6.78</v>
       </c>
@@ -7789,7 +7965,9 @@
       <c r="AV37" s="6" t="n"/>
       <c r="AW37" s="6" t="n"/>
       <c r="AX37" s="6" t="n"/>
-      <c r="AY37" s="6" t="n"/>
+      <c r="AY37" s="6" t="n">
+        <v>2.7</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
@@ -7831,7 +8009,11 @@
       <c r="K38" s="6" t="n">
         <v>65.78</v>
       </c>
-      <c r="L38" s="6" t="n"/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M38" s="6" t="n">
         <v>3.04</v>
       </c>
@@ -7980,7 +8162,9 @@
       <c r="AV38" s="6" t="n"/>
       <c r="AW38" s="6" t="n"/>
       <c r="AX38" s="6" t="n"/>
-      <c r="AY38" s="6" t="n"/>
+      <c r="AY38" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -8022,7 +8206,11 @@
       <c r="K39" s="6" t="n">
         <v>66.65000000000001</v>
       </c>
-      <c r="L39" s="6" t="n"/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8209,7 +8397,11 @@
       <c r="K40" s="6" t="n">
         <v>70.56999999999999</v>
       </c>
-      <c r="L40" s="6" t="n"/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M40" s="6" t="n">
         <v>5.5</v>
       </c>
@@ -8394,7 +8586,11 @@
       <c r="K41" s="6" t="n">
         <v>75.8</v>
       </c>
-      <c r="L41" s="6" t="n"/>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>old-old</t>
+        </is>
+      </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
           <t>未报告</t>
@@ -8547,7 +8743,9 @@
       <c r="AV41" s="6" t="n"/>
       <c r="AW41" s="6" t="n"/>
       <c r="AX41" s="6" t="n"/>
-      <c r="AY41" s="6" t="n"/>
+      <c r="AY41" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
@@ -8589,7 +8787,11 @@
       <c r="K42" s="6" t="n">
         <v>69.89</v>
       </c>
-      <c r="L42" s="6" t="n"/>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M42" s="6" t="n">
         <v>4.5</v>
       </c>
@@ -8734,7 +8936,9 @@
       <c r="AV42" s="6" t="n"/>
       <c r="AW42" s="6" t="n"/>
       <c r="AX42" s="6" t="n"/>
-      <c r="AY42" s="6" t="n"/>
+      <c r="AY42" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -8776,7 +8980,11 @@
       <c r="K43" s="6" t="n">
         <v>70.39</v>
       </c>
-      <c r="L43" s="6" t="n"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="n">
         <v>4.54</v>
       </c>
@@ -8915,7 +9123,9 @@
       <c r="AV43" s="6" t="n"/>
       <c r="AW43" s="6" t="n"/>
       <c r="AX43" s="6" t="n"/>
-      <c r="AY43" s="6" t="n"/>
+      <c r="AY43" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
@@ -8957,7 +9167,11 @@
       <c r="K44" s="6" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="L44" s="6" t="n"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M44" s="6" t="n">
         <v>2.89</v>
       </c>
@@ -9108,7 +9322,9 @@
       <c r="AV44" s="6" t="n"/>
       <c r="AW44" s="6" t="n"/>
       <c r="AX44" s="6" t="n"/>
-      <c r="AY44" s="6" t="n"/>
+      <c r="AY44" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -9150,7 +9366,11 @@
       <c r="K45" s="6" t="n">
         <v>70.39</v>
       </c>
-      <c r="L45" s="6" t="n"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M45" s="6" t="n">
         <v>4.54</v>
       </c>
@@ -9293,7 +9513,9 @@
       <c r="AV45" s="6" t="n"/>
       <c r="AW45" s="6" t="n"/>
       <c r="AX45" s="6" t="n"/>
-      <c r="AY45" s="6" t="n"/>
+      <c r="AY45" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
@@ -9335,7 +9557,11 @@
       <c r="K46" s="6" t="n">
         <v>86.8</v>
       </c>
-      <c r="L46" s="6" t="n"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>old-old</t>
+        </is>
+      </c>
       <c r="M46" s="6" t="n">
         <v>4</v>
       </c>
@@ -9480,7 +9706,9 @@
       <c r="AV46" s="6" t="n"/>
       <c r="AW46" s="6" t="n"/>
       <c r="AX46" s="6" t="n"/>
-      <c r="AY46" s="6" t="n"/>
+      <c r="AY46" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -9522,7 +9750,11 @@
       <c r="K47" s="6" t="n">
         <v>68.81</v>
       </c>
-      <c r="L47" s="6" t="n"/>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M47" s="6" t="n">
         <v>5.18</v>
       </c>
@@ -9705,7 +9937,11 @@
       <c r="K48" s="6" t="n">
         <v>72.86</v>
       </c>
-      <c r="L48" s="6" t="n"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M48" s="6" t="n">
         <v>5.14</v>
       </c>
@@ -9852,7 +10088,9 @@
       <c r="AV48" s="6" t="n"/>
       <c r="AW48" s="6" t="n"/>
       <c r="AX48" s="6" t="n"/>
-      <c r="AY48" s="6" t="n"/>
+      <c r="AY48" s="6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -9894,7 +10132,11 @@
       <c r="K49" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="L49" s="6" t="n"/>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M49" s="6" t="n">
         <v>4</v>
       </c>
@@ -10037,7 +10279,9 @@
       <c r="AV49" s="6" t="n"/>
       <c r="AW49" s="6" t="n"/>
       <c r="AX49" s="6" t="n"/>
-      <c r="AY49" s="6" t="n"/>
+      <c r="AY49" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
@@ -10079,7 +10323,11 @@
       <c r="K50" s="6" t="n">
         <v>69.3</v>
       </c>
-      <c r="L50" s="6" t="n"/>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M50" s="6" t="n">
         <v>6.9</v>
       </c>
@@ -10226,7 +10474,9 @@
       <c r="AV50" s="6" t="n"/>
       <c r="AW50" s="6" t="n"/>
       <c r="AX50" s="6" t="n"/>
-      <c r="AY50" s="6" t="n"/>
+      <c r="AY50" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -10413,7 +10663,9 @@
       <c r="AV51" s="6" t="n"/>
       <c r="AW51" s="6" t="n"/>
       <c r="AX51" s="6" t="n"/>
-      <c r="AY51" s="6" t="n"/>
+      <c r="AY51" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
@@ -10455,7 +10707,11 @@
       <c r="K52" s="6" t="n">
         <v>75.3</v>
       </c>
-      <c r="L52" s="6" t="n"/>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>old-old</t>
+        </is>
+      </c>
       <c r="M52" s="6" t="n">
         <v>6.5</v>
       </c>
@@ -10642,7 +10898,11 @@
       <c r="K53" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="L53" s="6" t="n"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M53" s="6" t="n">
         <v>3.5</v>
       </c>
@@ -10791,7 +11051,9 @@
       <c r="AV53" s="6" t="n"/>
       <c r="AW53" s="6" t="n"/>
       <c r="AX53" s="6" t="n"/>
-      <c r="AY53" s="6" t="n"/>
+      <c r="AY53" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
@@ -10833,7 +11095,11 @@
       <c r="K54" s="6" t="n">
         <v>69.58</v>
       </c>
-      <c r="L54" s="6" t="n"/>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M54" s="6" t="n">
         <v>7.04</v>
       </c>
@@ -10978,7 +11244,9 @@
       <c r="AV54" s="6" t="n"/>
       <c r="AW54" s="6" t="n"/>
       <c r="AX54" s="6" t="n"/>
-      <c r="AY54" s="6" t="n"/>
+      <c r="AY54" s="6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -11020,7 +11288,11 @@
       <c r="K55" s="6" t="n">
         <v>68.44</v>
       </c>
-      <c r="L55" s="6" t="n"/>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M55" s="6" t="n">
         <v>4</v>
       </c>
@@ -11167,7 +11439,9 @@
       <c r="AV55" s="6" t="n"/>
       <c r="AW55" s="6" t="n"/>
       <c r="AX55" s="6" t="n"/>
-      <c r="AY55" s="6" t="n"/>
+      <c r="AY55" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -11209,7 +11483,11 @@
       <c r="K56" s="6" t="n">
         <v>61.86</v>
       </c>
-      <c r="L56" s="6" t="n"/>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M56" s="6" t="n">
         <v>5.37</v>
       </c>
@@ -11364,7 +11642,9 @@
       <c r="AV56" s="6" t="n"/>
       <c r="AW56" s="6" t="n"/>
       <c r="AX56" s="6" t="n"/>
-      <c r="AY56" s="6" t="n"/>
+      <c r="AY56" s="6" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -11406,7 +11686,11 @@
       <c r="K57" s="6" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="L57" s="6" t="n"/>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M57" s="6" t="n">
         <v>3.99</v>
       </c>
@@ -11553,7 +11837,9 @@
       <c r="AV57" s="6" t="n"/>
       <c r="AW57" s="6" t="n"/>
       <c r="AX57" s="6" t="n"/>
-      <c r="AY57" s="6" t="n"/>
+      <c r="AY57" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
@@ -11595,7 +11881,11 @@
       <c r="K58" s="6" t="n">
         <v>70.64</v>
       </c>
-      <c r="L58" s="6" t="n"/>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>young-old</t>
+        </is>
+      </c>
       <c r="M58" s="6" t="n">
         <v>5.47</v>
       </c>
@@ -11742,7 +12032,9 @@
       <c r="AV58" s="6" t="n"/>
       <c r="AW58" s="6" t="n"/>
       <c r="AX58" s="6" t="n"/>
-      <c r="AY58" s="6" t="n"/>
+      <c r="AY58" s="6" t="n">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/paper-01/04-extract/数据_6_数据提取表_v2.xlsx
+++ b/projects/paper-01/04-extract/数据_6_数据提取表_v2.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据提取" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="偏倚风险评估_RoB" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核查报告" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +43,31 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00375623"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -75,8 +99,28 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF3FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -98,11 +142,25 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +199,51 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13718,4 +13821,474 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>📊 数据核查报告 — Paper-01 数据提取表 v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>生成时间：2026-04-04 22:46    数据来源：数据_6_数据提取表_v2.xlsx（第3行起，共56行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>一、计算字段完成情况</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>成功计算</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>留空（缺失）</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>训练频率(次/周)</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="21">
+        <f>总次数÷训练周数，保留1位小数</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>年龄段分类</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>young-old(≤75岁)：42篇 / old-old(&gt;75岁)：7篇</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>二、异常值清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>第一作者</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>异常字段</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>异常值</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>正常范围</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>建议核查</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>✅  未发现异常值</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>三、缺失值统计（关键字段）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>缺失篇数</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>缺失文献（作者 年份）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>年龄均值</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>样本量N</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>训练总次数</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>C 2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>训练周数</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>C 2016; EM 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>每次时长(分钟)</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>SH 2014; SJ 2023; S 2017; E 2025; C 2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>性别(%女)</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>CN 2014; A 2017; SJ 2023; JA 2017; E 2025; VM 2018; VM 2017; E 2017; D 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>教育年限(年)</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>SH 2014; S 2022; Günther 2003; M 2008; SJ 2023; JA 2017; E 2025; LP 2013; VM 2018; VM 2017; K 2012; D 2022; C 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>四、需要人工核查的优先列表（综合异常值+关键字段缺失）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>第一作者</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="27" t="n">
+        <v>51</v>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>缺失：训练总次数；缺失：训练周数；缺失：每次时长(分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="27" t="n">
+        <v>32</v>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>缺失：每次时长(分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>SJ</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>缺失：每次时长(分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>41</v>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>缺失：每次时长(分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>44</v>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>缺失：每次时长(分钟)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="28" t="n">
+        <v>57</v>
+      </c>
+      <c r="C30" s="28" t="inlineStr">
+        <is>
+          <t>EM</t>
+        </is>
+      </c>
+      <c r="D30" s="28" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E30" s="29" t="inlineStr">
+        <is>
+          <t>缺失：训练周数</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>